--- a/daily_matches/job_matches_2026-05-03.xlsx
+++ b/daily_matches/job_matches_2026-05-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,455 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Data Engineer (DataOps &amp; Infrastructure Focus)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Hugging Face, ChromaDB, Prompt Engineering, TensorFlow</t>
+          <t>RAG, S3, Glue, Redshift, CI/CD, Terraform, Git, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27ca12ec8e3403ed</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, TensorFlow, PyTorch, spaCy, NLTK</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f110f42052fd5fe3</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Senior GCP Kubernetes Engineer</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, TensorFlow, PyTorch, spaCy, NLTK</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44bf0f9c23ef7ab5</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>GCP Support Associate</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Pinecone, Prompt Engineering, BigQuery, FastAPI, BigQuery, Python</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f29f41f0a76287</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Wolters Kluwer</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Saint Cloud, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, Docker, AKS, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5564e741df81f16a</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, XGBoost, MLflow, Docker, Kubernetes, CI/CD, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f50be5ebddbfdcc</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AI Agents Applied Engineer - Senior Associate</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22e0831520cef182</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>GCP Support Associate</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Data Lake, Dataflow, Snowflake, BigQuery, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Forward Deployed Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Growth Protocol</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, BigQuery, FastAPI, Docker, Snowflake, BigQuery, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4496f684c0e2117</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Forward Deployed Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Growth Protocol</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, BigQuery, FastAPI, Docker, Snowflake, BigQuery, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa353bc610802c7a</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>GCP AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Copilot, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad6c0ae45d10b9b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Cloud Engineer - NAVSUP OIS - Remote</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>General Dynamics Information Technology</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Docker, CI/CD, Jenkins, Terraform, Git, Kafka, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd256b803c4afebd</t>
+          <t>https://www.indeed.com/viewjob?jk=6125421c57f16e3e</t>
         </is>
       </c>
     </row>
